--- a/data/sku_mapping.xlsx
+++ b/data/sku_mapping.xlsx
@@ -1,45 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vacha\Desktop\I'\price-dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6F2D702-CCDD-40AC-9E92-388969B5360B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067995DF-7B42-4DD4-A5C9-BE2955939EE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{83D97BEF-1294-46BF-9E98-4715218D3894}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="196">
   <si>
     <t>SKU</t>
   </si>
@@ -59,432 +40,573 @@
     <t>XM1000</t>
   </si>
   <si>
+    <t>Men's 'Flex Collective' Lightweight Training Tee</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/tshirts/ten+x+you/ten-x-you-lightweight-buttery-feel-gym-and-training-t-shirt/39109690/buy</t>
+  </si>
+  <si>
     <t>XM1003</t>
   </si>
   <si>
+    <t>Men's Long Distance Running Tee</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/tshirts/ten+x+you/ten-x-you-run-the-world-lightweight-running-t-shirt/39109691/buy</t>
+  </si>
+  <si>
     <t>XM1004</t>
   </si>
   <si>
+    <t>Men's Loose Fit Tee</t>
+  </si>
+  <si>
+    <t>https://www.myntra.com/tshirts/ten+x+you/ten-x-you-relaxed-fit-sport-to-street-t-shirt/39062509/buy</t>
+  </si>
+  <si>
     <t>XM1005</t>
-  </si>
-  <si>
-    <t>XM1009</t>
-  </si>
-  <si>
-    <t>XM1012</t>
-  </si>
-  <si>
-    <t>XM1045</t>
-  </si>
-  <si>
-    <t>XM2000</t>
-  </si>
-  <si>
-    <t>XM2004</t>
-  </si>
-  <si>
-    <t>XM2005</t>
-  </si>
-  <si>
-    <t>XM2006</t>
-  </si>
-  <si>
-    <t>XM3006</t>
-  </si>
-  <si>
-    <t>XM3007</t>
-  </si>
-  <si>
-    <t>XM3007T</t>
-  </si>
-  <si>
-    <t>Mens Tapered fit Jogger (tall)</t>
-  </si>
-  <si>
-    <t>XM5005</t>
-  </si>
-  <si>
-    <t>XM5006</t>
-  </si>
-  <si>
-    <t>XM5007</t>
-  </si>
-  <si>
-    <t>XM5008</t>
-  </si>
-  <si>
-    <t>XM5009</t>
-  </si>
-  <si>
-    <t>XW1000</t>
-  </si>
-  <si>
-    <t>XW1003</t>
-  </si>
-  <si>
-    <t>XW1009</t>
-  </si>
-  <si>
-    <t>XW1010</t>
-  </si>
-  <si>
-    <t>XW1011</t>
-  </si>
-  <si>
-    <t>XW1012</t>
-  </si>
-  <si>
-    <t>XW1014</t>
-  </si>
-  <si>
-    <t>XW2003</t>
-  </si>
-  <si>
-    <t>XW2004</t>
-  </si>
-  <si>
-    <t>XW2005</t>
-  </si>
-  <si>
-    <t>XW3007R</t>
-  </si>
-  <si>
-    <t>XW3007T</t>
-  </si>
-  <si>
-    <t>XW3010R</t>
-  </si>
-  <si>
-    <t>Flowstate Kick Flare Pants</t>
-  </si>
-  <si>
-    <t>XW3010T</t>
-  </si>
-  <si>
-    <t>XW3013R</t>
-  </si>
-  <si>
-    <t>Flowstate Flare Pants</t>
-  </si>
-  <si>
-    <t>XW3013T</t>
-  </si>
-  <si>
-    <t>XW3014R</t>
-  </si>
-  <si>
-    <t>XW3014T</t>
-  </si>
-  <si>
-    <t>XW3016</t>
-  </si>
-  <si>
-    <t>XW5002</t>
-  </si>
-  <si>
-    <t>XW5003</t>
-  </si>
-  <si>
-    <t>XW5005</t>
-  </si>
-  <si>
-    <t>XW5006</t>
-  </si>
-  <si>
-    <t>XW5007</t>
-  </si>
-  <si>
-    <t>XU002</t>
-  </si>
-  <si>
-    <t>XU003</t>
-  </si>
-  <si>
-    <t>XU004</t>
-  </si>
-  <si>
-    <t>XU005</t>
-  </si>
-  <si>
-    <t>XU006</t>
-  </si>
-  <si>
-    <t>XU007</t>
-  </si>
-  <si>
-    <t>XU008</t>
-  </si>
-  <si>
-    <t>XU009</t>
-  </si>
-  <si>
-    <t>XU011</t>
-  </si>
-  <si>
-    <t>XU012</t>
-  </si>
-  <si>
-    <t>XU013</t>
-  </si>
-  <si>
-    <t>XU014</t>
-  </si>
-  <si>
-    <t>XU015</t>
-  </si>
-  <si>
-    <t>XU016</t>
-  </si>
-  <si>
-    <t>XU017</t>
-  </si>
-  <si>
-    <t>XU018</t>
-  </si>
-  <si>
-    <t>XU019</t>
-  </si>
-  <si>
-    <t>XU089</t>
-  </si>
-  <si>
-    <t>XU098</t>
-  </si>
-  <si>
-    <t>SRLB</t>
-  </si>
-  <si>
-    <t>SRTBAT2026</t>
-  </si>
-  <si>
-    <t>XA1001</t>
-  </si>
-  <si>
-    <t>XA1003</t>
-  </si>
-  <si>
-    <t>XA1006</t>
-  </si>
-  <si>
-    <t>XA2002</t>
-  </si>
-  <si>
-    <t>XA2003</t>
-  </si>
-  <si>
-    <t>XA2006</t>
-  </si>
-  <si>
-    <t>XA2007</t>
-  </si>
-  <si>
-    <t>XA2008</t>
-  </si>
-  <si>
-    <t>XA2009</t>
-  </si>
-  <si>
-    <t>XU001</t>
-  </si>
-  <si>
-    <t>XU010</t>
-  </si>
-  <si>
-    <t>Men's 'Flex Collective' Lightweight Training Tee</t>
-  </si>
-  <si>
-    <t>Men's Long Distance Running Tee</t>
-  </si>
-  <si>
-    <t>Men's Loose Fit Tee</t>
   </si>
   <si>
     <t xml:space="preserve">Men's Relaxed Fit Tee
 </t>
   </si>
   <si>
+    <t>XM1009</t>
+  </si>
+  <si>
     <t>Men's Street Sport Oversized Tee</t>
   </si>
   <si>
+    <t>https://www.myntra.com/tshirts/ten+x+you/ten-x-you-oversized-sport-to-street-high-gsm-pure-cotton-t-shirt/39062483/buy</t>
+  </si>
+  <si>
+    <t>XM1012</t>
+  </si>
+  <si>
     <t>Men's Ultra-lightweight Tempo Running Tee</t>
   </si>
   <si>
+    <t>https://www.myntra.com/tshirts/ten+x+you/ten-x-you-lightweight-melange-running-t-shirt/39109695/buy</t>
+  </si>
+  <si>
+    <t>XM1045</t>
+  </si>
+  <si>
+    <t>XM2000</t>
+  </si>
+  <si>
     <t>Men's Ultra-lightweight Tempo Running Tank</t>
+  </si>
+  <si>
+    <t>XM2004</t>
   </si>
   <si>
     <t xml:space="preserve">Men's Relaxed Fit Tank
 </t>
   </si>
   <si>
+    <t>https://www.myntra.com/tshirts/ten+x+you/ten-x-you-sport-to-street-relaxed-fit-tank-t-shirt/39115461/buy</t>
+  </si>
+  <si>
+    <t>XM2005</t>
+  </si>
+  <si>
     <t>Men's Muscle Tank</t>
   </si>
   <si>
+    <t>XM2006</t>
+  </si>
+  <si>
     <t>Men's Sports Tank</t>
   </si>
   <si>
+    <t>https://www.myntra.com/tshirts/ten+x+you/ten-x-you-sport-to-street-drop-shoulder-pure-cotton-tank-t-shirt/39115462/buy</t>
+  </si>
+  <si>
+    <t>XM3006</t>
+  </si>
+  <si>
     <t>Men's UberSoft Straight Fit Jogger</t>
   </si>
   <si>
+    <t>XM3007</t>
+  </si>
+  <si>
     <t>Men's UberSoft Training Joggers</t>
   </si>
   <si>
+    <t>XM3007T</t>
+  </si>
+  <si>
+    <t>Mens Tapered fit Jogger (tall)</t>
+  </si>
+  <si>
+    <t>XM5005</t>
+  </si>
+  <si>
     <t>Men's UberSoft Relaxed Shorts</t>
   </si>
   <si>
+    <t>https://www.myntra.com/shorts/ten+x+you/ten-x-you-men-ubersoft-relaxed-shorts/41983270/buy</t>
+  </si>
+  <si>
+    <t>https://www.ajio.com/ten-x-you-men-relaxed-fit-running-shorts/p/469817546_black?</t>
+  </si>
+  <si>
+    <t>XM5006</t>
+  </si>
+  <si>
     <t>Men's 'Flex Collective' 7" Training Shorts</t>
   </si>
   <si>
+    <t>https://www.myntra.com/shorts/ten+x+you/ten-x-you-women-flex-collective-6-training-shorts/39109746/buy</t>
+  </si>
+  <si>
+    <t>XM5007</t>
+  </si>
+  <si>
     <t>Men's 5" Lined Running Shorts</t>
   </si>
   <si>
+    <t>https://www.myntra.com/shorts/ten+x+you/ten-x-you-men-run-the-world-5-lined-running-shorts/39062448/buy</t>
+  </si>
+  <si>
+    <t>https://www.ajio.com/ten-x-you-men-regular-fit-running-shorts/p/469817547_grey?</t>
+  </si>
+  <si>
+    <t>XM5008</t>
+  </si>
+  <si>
     <t>Men's 7" Lined Running Shorts</t>
   </si>
   <si>
+    <t>XM5009</t>
+  </si>
+  <si>
     <t>Men's Shorts</t>
   </si>
   <si>
+    <t>https://www.myntra.com/shorts/ten+x+you/ten-x-you-men-365-sport-to-street-shorts/39062443/buy</t>
+  </si>
+  <si>
+    <t>XW1000</t>
+  </si>
+  <si>
     <t>Women's 'Flex Collective' Lightweight Training Tee</t>
   </si>
   <si>
+    <t>XW1003</t>
+  </si>
+  <si>
     <t>Women's Long Distance Running Tee</t>
   </si>
   <si>
+    <t>XW1009</t>
+  </si>
+  <si>
     <t>Women's Street Sport Oversized Tee</t>
   </si>
   <si>
+    <t>XW1010</t>
+  </si>
+  <si>
     <t>Women's Relaxed Fit Tee</t>
   </si>
   <si>
+    <t>XW1011</t>
+  </si>
+  <si>
     <t>Women's Slim Fit Tee</t>
   </si>
   <si>
+    <t>https://www.myntra.com/tshirts/ten+x+you/ten-x-you-slim-fit-soft-athleisure-t-shirt/39062511/buy</t>
+  </si>
+  <si>
+    <t>https://www.ajio.com/ten-x-you-women-logo-print-slim-fit-crew-neck-t-shirt/p/469817560_brown?</t>
+  </si>
+  <si>
+    <t>XW1012</t>
+  </si>
+  <si>
     <t>Women's Ultra-lightweight Tempo Running Tee</t>
   </si>
   <si>
+    <t>XW1014</t>
+  </si>
+  <si>
+    <t>XW2003</t>
+  </si>
+  <si>
     <t>Women's Muscle Tank</t>
   </si>
   <si>
+    <t>https://www.myntra.com/tshirts/ten+x+you/ten-x-you-sport-to-street-muscle-tank-t-shirt-with-big-armhole/39118256/buy</t>
+  </si>
+  <si>
+    <t>XW2004</t>
+  </si>
+  <si>
     <t xml:space="preserve">Women's Ribbed Tank </t>
   </si>
   <si>
+    <t>https://www.myntra.com/tops/ten+x+you/ten-x-you-ultra-soft-ribbed-sleeveless-moisture-wicking-tank-top/39118259/buy</t>
+  </si>
+  <si>
+    <t>https://www.ajio.com/ten-x-you-women-ribbed-regular-fit-tank-top/p/469817562_copper?</t>
+  </si>
+  <si>
+    <t>XW2005</t>
+  </si>
+  <si>
     <t>Women's Ultra-lightweight Tempo Running Tank</t>
   </si>
   <si>
+    <t>https://www.ajio.com/ten-x-you-women-regular-fit-crew-neck-running-tank-t-shirt/p/469817556_blue?</t>
+  </si>
+  <si>
+    <t>XW3007R</t>
+  </si>
+  <si>
     <t>Flow-state Mid Impact Leggings</t>
   </si>
   <si>
+    <t>https://www.myntra.com/leggings/ten+x+you/ten-x-you-women-ankle-length-leggings/41371883/buy</t>
+  </si>
+  <si>
+    <t>XW3007T</t>
+  </si>
+  <si>
+    <t>XW3010R</t>
+  </si>
+  <si>
+    <t>Flowstate Kick Flare Pants</t>
+  </si>
+  <si>
+    <t>XW3010T</t>
+  </si>
+  <si>
+    <t>XW3013R</t>
+  </si>
+  <si>
+    <t>Flowstate Flare Pants</t>
+  </si>
+  <si>
+    <t>XW3013T</t>
+  </si>
+  <si>
+    <t>XW3014R</t>
+  </si>
+  <si>
     <t>Sculptex - High Impact Leggings</t>
   </si>
   <si>
+    <t>XW3014T</t>
+  </si>
+  <si>
+    <t>XW3016</t>
+  </si>
+  <si>
     <t>Women's UberSoft Straight Fit Joggers</t>
   </si>
   <si>
+    <t>https://www.myntra.com/track-pants/ten+x+you/ten-x-you-women-ubersoft-straight-fit-joggers/41868324/buy</t>
+  </si>
+  <si>
+    <t>XW5002</t>
+  </si>
+  <si>
     <t>Women's 4" Lined Running Shorts</t>
   </si>
   <si>
+    <t>https://www.myntra.com/shorts/ten+x+you/ten-x-you-women-run-the-world-4-lined-running-shorts/39109742/buy</t>
+  </si>
+  <si>
+    <t>XW5003</t>
+  </si>
+  <si>
     <t>Women's 'Flex Collective' 6" Training Shorts</t>
   </si>
   <si>
+    <t>https://www.ajio.com/ten-x-you-women-training-shorts/p/469817552_blue?</t>
+  </si>
+  <si>
+    <t>XW5005</t>
+  </si>
+  <si>
     <t>Women's 6" Lined Running Shorts</t>
   </si>
   <si>
+    <t>XW5006</t>
+  </si>
+  <si>
     <t xml:space="preserve">Women's Shorts </t>
   </si>
   <si>
+    <t>https://www.myntra.com/shorts/ten+x+you/ten-x-you-women-365-sportstyle-shorts/39109736/buy</t>
+  </si>
+  <si>
+    <t>XW5007</t>
+  </si>
+  <si>
     <t>Sculptex High Impact Biker Shorts</t>
   </si>
   <si>
+    <t>XU002</t>
+  </si>
+  <si>
     <t xml:space="preserve">Centurion Pro Batsman Shoe </t>
   </si>
   <si>
+    <t>https://www.ajio.com/ten-x-you-men-centurion-pro-cricket-shoes/p/469817203_white?</t>
+  </si>
+  <si>
+    <t>XU003</t>
+  </si>
+  <si>
     <t xml:space="preserve">Switch Hit Semi-Pro Cricket Shoe </t>
   </si>
   <si>
+    <t>https://www.myntra.com/sports-shoes/ten+x+you/ten-x-you-unisex-switch-fan-edit-20-multi-sport-shoes/40949265/buy</t>
+  </si>
+  <si>
+    <t>https://www.ajio.com/ten-x-you-unisex-switch-fan-edit-2-0-multi-sport-sneakers/p/469817213_blue?</t>
+  </si>
+  <si>
+    <t>XU004</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unisex Switch Street Multi-Sport Sneaker </t>
   </si>
   <si>
+    <t>https://www.myntra.com/sports-shoes/ten+x+you/ten-x-you-unisex-switch-og-sports-shoes/39073823/buy</t>
+  </si>
+  <si>
+    <t>XU005</t>
+  </si>
+  <si>
     <t>Unisex Aeonic Running Shoe</t>
   </si>
   <si>
+    <t>https://www.myntra.com/sports-shoes/ten+x+you/ten-x-you-unisex-aeonic-recovery-running-shoes-with-cushioned-arch-support/39048046/buy</t>
+  </si>
+  <si>
+    <t>https://www.ajio.com/ten-x-you-unisex-aeonic-running-shoes/p/469817206_green?</t>
+  </si>
+  <si>
+    <t>XU006</t>
+  </si>
+  <si>
     <t>Unisex Zenflo Walking Shoe</t>
   </si>
   <si>
+    <t>https://www.myntra.com/sports-shoes/ten+x+you/ten-x-you-unisex-zenflo-arch-support-walking-slip-on-shoes/39073887/buy</t>
+  </si>
+  <si>
+    <t>https://www.ajio.com/ten-x-you-unisex-zenflo-walking-shoes/p/469817207_black?</t>
+  </si>
+  <si>
+    <t>XU007</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unisex Crossover Slip On Sneaker </t>
   </si>
   <si>
+    <t>https://www.myntra.com/sports-shoes/ten+x+you/ten-x-you-unisex-crossover-light-gym-to-street-slip-on-sneakers-with-arch-support/39073895/buy</t>
+  </si>
+  <si>
+    <t>https://www.ajio.com/ten-x-you-unisex-crossover-slip-on-sneakers/p/469817208_blackwhite?</t>
+  </si>
+  <si>
+    <t>XU008</t>
+  </si>
+  <si>
     <t>Unisex Sundowner Denim Sneaker</t>
   </si>
   <si>
+    <t>https://www.myntra.com/casual-shoes/ten+x+you/ten-x-you-unisex-sundowner-denim-lifestyle-sneakers/39073847/buy</t>
+  </si>
+  <si>
+    <t>https://www.ajio.com/ten-x-you-unisex-sundowner-denim-sneakers/p/469817209_green?</t>
+  </si>
+  <si>
+    <t>XU009</t>
+  </si>
+  <si>
     <t>NOX Legacy Sneaker</t>
   </si>
   <si>
+    <t>https://www.myntra.com/casual-shoes/ten+x+you/ten-x-you-unisex-sachins-nox-legacy-lace-up-leather-sneakers/39073863/buy</t>
+  </si>
+  <si>
+    <t>https://www.ajio.com/ten-x-you-men-nox-legacy-sneakers/p/469817210_black?</t>
+  </si>
+  <si>
+    <t>XU011</t>
+  </si>
+  <si>
     <t>All-rounder Cricket Shoe</t>
   </si>
   <si>
+    <t>https://www.myntra.com/sports-shoes/ten+x+you/ten-x-you-all-rounder-cricket-shoe---ultra-lightweight-full-rubber-studs-for-superior-grip/41983950/buy</t>
+  </si>
+  <si>
+    <t>https://www.ajio.com/ten-x-you-men-all-rounder-cricket-shoes/p/469817211_white?</t>
+  </si>
+  <si>
+    <t>XU012</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unisex Switch OG 2.0 Multi-Sport Sneaker </t>
   </si>
   <si>
+    <t>https://www.myntra.com/sports-shoes/ten+x+you/ten-x-you-all-rounder-cricket-shoe---ultra-lightweight-full-rubber-studs-for-superior-grip/40099354/buy</t>
+  </si>
+  <si>
+    <t>XU013</t>
+  </si>
+  <si>
     <t>Unisex Switch Fan Edit- Bangalore Chapter</t>
   </si>
   <si>
+    <t>https://www.myntra.com/sports-shoes/ten+x+you/ten-x-you-unisex-switch-fan-edit-20-multi-sport-sneaker/40949260/buy</t>
+  </si>
+  <si>
+    <t>XU014</t>
+  </si>
+  <si>
     <t>Unisex Reset Slides</t>
   </si>
   <si>
+    <t>https://www.ajio.com/ten-x-you-unisex-logo-print-reset-slides/p/469817214_limegreen?</t>
+  </si>
+  <si>
+    <t>XU015</t>
+  </si>
+  <si>
     <t>Unisex Reset Velcro Slides</t>
   </si>
   <si>
+    <t>https://www.myntra.com/flip-flops/ten+x+you/ten-x-you-unisex-velcro-sliders/42100938/buy</t>
+  </si>
+  <si>
+    <t>XU016</t>
+  </si>
+  <si>
     <t>Pivot Thong Flip Flops</t>
   </si>
   <si>
+    <t>https://www.myntra.com/flip-flops/ten+x+you/ten-x-you-unisex-thong-flip-flops/42100939/buy</t>
+  </si>
+  <si>
+    <t>XU017</t>
+  </si>
+  <si>
     <t>All-rounder Swing Cricket Shoe</t>
   </si>
   <si>
+    <t>https://www.myntra.com/sports-shoes/ten+x+you/ten-x-you-men-all-rounder-cricket-shoe/40099352/buy</t>
+  </si>
+  <si>
+    <t>XU018</t>
+  </si>
+  <si>
     <t>Reboot Dual density Slides</t>
   </si>
   <si>
+    <t>XU019</t>
+  </si>
+  <si>
     <t>Youngstar kids shoe</t>
   </si>
   <si>
+    <t>XU089</t>
+  </si>
+  <si>
     <t>Nox - The Debut Sneaker</t>
   </si>
   <si>
+    <t>XU098</t>
+  </si>
+  <si>
     <t>NOX - The Desert Storm</t>
   </si>
   <si>
+    <t>SRLB</t>
+  </si>
+  <si>
     <t>Signed Red Leather Balls</t>
   </si>
   <si>
+    <t>SRTBAT2026</t>
+  </si>
+  <si>
     <t>Signed Bat</t>
   </si>
   <si>
+    <t>XA1001</t>
+  </si>
+  <si>
     <t xml:space="preserve">Running Cap </t>
   </si>
   <si>
+    <t>XA1003</t>
+  </si>
+  <si>
     <t>Club Cap</t>
   </si>
   <si>
+    <t>https://www.myntra.com/caps/ten+x+you/ten-x-you-unisex-club-baseball-cap/39208069/buy</t>
+  </si>
+  <si>
+    <t>XA1006</t>
+  </si>
+  <si>
     <t>Trucker Cap</t>
   </si>
   <si>
+    <t>XA2002</t>
+  </si>
+  <si>
     <t>Everyday Low Ankle Socks</t>
   </si>
   <si>
+    <t>XA2003</t>
+  </si>
+  <si>
     <t>Sports High Ankle Socks</t>
   </si>
   <si>
+    <t>XA2006</t>
+  </si>
+  <si>
     <t>Everyday High Ankle Socks</t>
   </si>
   <si>
+    <t>XA2007</t>
+  </si>
+  <si>
     <t>Cricket Crew Socks</t>
   </si>
   <si>
+    <t>XA2008</t>
+  </si>
+  <si>
     <t xml:space="preserve">Running Low Ankle Socks </t>
   </si>
   <si>
+    <t>XA2009</t>
+  </si>
+  <si>
     <t xml:space="preserve">Running High Ankle Socks </t>
   </si>
   <si>
+    <t>XU001</t>
+  </si>
+  <si>
     <t>Footwork Pulse Cricket Insoles</t>
+  </si>
+  <si>
+    <t>XU010</t>
   </si>
   <si>
     <t xml:space="preserve">Footwork Grip Spikes </t>
@@ -494,7 +616,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -505,6 +627,14 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -524,10 +654,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -535,10 +666,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -870,18 +1005,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B95AA84A-55CC-4B67-95FF-CB6CE4E72EB0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E76"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="41.88671875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="41.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -894,133 +1029,155 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C2" s="1"/>
+      <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C3" s="1"/>
+        <v>8</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="C4" s="1"/>
+        <v>11</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="C5" s="1"/>
+        <v>14</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="216" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C6" s="1"/>
+        <v>16</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C7" s="1"/>
+        <v>19</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C8" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C9" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C10" s="1"/>
+        <v>25</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="216" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="C11" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C12" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>93</v>
+        <v>33</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -1028,10 +1185,10 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>94</v>
+        <v>35</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -1039,505 +1196,625 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>19</v>
+        <v>37</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
+        <v>39</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C17" s="1"/>
+        <v>43</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="E18" s="1"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
+        <v>50</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
+        <v>52</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="C21" s="1"/>
+        <v>55</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="C22" s="1"/>
+        <v>57</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" ht="216" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="C23" s="1"/>
+        <v>59</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="C24" s="1"/>
+        <v>61</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
+        <v>63</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="E25" s="1"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C26" s="1"/>
+        <v>67</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="C27" s="1"/>
+        <v>69</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" ht="216" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="C28" s="1"/>
+        <v>70</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" ht="216" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
+        <v>73</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="E29" s="1"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
+        <v>77</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="E30" s="1"/>
     </row>
-    <row r="31" spans="1:5" ht="27" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="C31" s="1"/>
+        <v>80</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="1:5" ht="27" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="C32" s="1"/>
+        <v>83</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
     </row>
-    <row r="33" spans="1:5" ht="27" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>38</v>
+        <v>84</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>85</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
     </row>
-    <row r="34" spans="1:5" ht="27" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>38</v>
+        <v>86</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>85</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
     </row>
-    <row r="35" spans="1:5" ht="27" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>41</v>
+        <v>87</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>88</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
     </row>
-    <row r="36" spans="1:5" ht="27" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>41</v>
+        <v>89</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>88</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
-    <row r="37" spans="1:5" ht="27" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C37" s="1"/>
+        <v>90</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
     </row>
-    <row r="38" spans="1:5" ht="27" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C38" s="1"/>
+        <v>92</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="C39" s="1"/>
+        <v>93</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>95</v>
+      </c>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="C40" s="1"/>
+        <v>96</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>98</v>
+      </c>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
+        <v>99</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="E41" s="1"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C42" s="1"/>
+        <v>102</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>98</v>
+      </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
+        <v>104</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="E43" s="1"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>116</v>
+        <v>107</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>108</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B45" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E45" s="1"/>
+    </row>
+    <row r="46" spans="1:5" ht="216" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E46" s="1"/>
+    </row>
+    <row r="47" spans="1:5" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B46" s="4" t="s">
+      <c r="C47" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B47" s="4" t="s">
+      <c r="D47" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E47" s="1"/>
+    </row>
+    <row r="48" spans="1:5" ht="259.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
+      <c r="C48" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>122</v>
+      </c>
       <c r="E48" s="1"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
+        <v>123</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>126</v>
+      </c>
       <c r="E49" s="1"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" ht="244.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
+        <v>127</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>130</v>
+      </c>
       <c r="E50" s="1"/>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" ht="201.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
+        <v>131</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>134</v>
+      </c>
       <c r="E51" s="1"/>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
+        <v>135</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="E52" s="1"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" ht="273.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="C53" s="1"/>
-      <c r="D53" s="1"/>
+        <v>139</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>142</v>
+      </c>
       <c r="E53" s="1"/>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
+        <v>143</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="E54" s="1"/>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" ht="216" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C55" s="1"/>
-      <c r="D55" s="1"/>
+        <v>146</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="E55" s="1"/>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>128</v>
+        <v>149</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>150</v>
       </c>
       <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
+      <c r="D56" s="1" t="s">
+        <v>151</v>
+      </c>
       <c r="E56" s="1"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
+        <v>152</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>151</v>
+      </c>
       <c r="E57" s="1"/>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="C58" s="1"/>
+        <v>155</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" ht="259.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="C59" s="1"/>
-      <c r="D59" s="1"/>
+        <v>158</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>142</v>
+      </c>
       <c r="E59" s="1"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>132</v>
+        <v>161</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>162</v>
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
@@ -1545,10 +1822,10 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>133</v>
+        <v>163</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>164</v>
       </c>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
@@ -1556,10 +1833,10 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>134</v>
+        <v>165</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>166</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
@@ -1567,10 +1844,10 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>135</v>
+        <v>167</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>168</v>
       </c>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
@@ -1578,21 +1855,21 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>136</v>
+        <v>169</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
     </row>
-    <row r="65" spans="1:5" ht="27" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B65" s="4" t="s">
-        <v>137</v>
+        <v>171</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>172</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
@@ -1600,32 +1877,34 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B66" s="4" t="s">
-        <v>138</v>
+        <v>173</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="C67" s="1"/>
+        <v>175</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>177</v>
+      </c>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>140</v>
+        <v>178</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
@@ -1633,10 +1912,10 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>141</v>
+        <v>180</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>181</v>
       </c>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
@@ -1644,10 +1923,10 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>142</v>
+        <v>182</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>183</v>
       </c>
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
@@ -1655,10 +1934,10 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B71" s="4" t="s">
-        <v>143</v>
+        <v>184</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>185</v>
       </c>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
@@ -1666,10 +1945,10 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>144</v>
+        <v>186</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>187</v>
       </c>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
@@ -1677,10 +1956,10 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B73" s="4" t="s">
-        <v>145</v>
+        <v>188</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>189</v>
       </c>
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
@@ -1688,10 +1967,10 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>146</v>
+        <v>190</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>191</v>
       </c>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
@@ -1699,10 +1978,10 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>147</v>
+        <v>192</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>193</v>
       </c>
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
@@ -1710,16 +1989,23 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B76" s="4" t="s">
-        <v>148</v>
+        <v>194</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>195</v>
       </c>
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="C18" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="C19" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/sku_mapping.xlsx
+++ b/data/sku_mapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vacha\Desktop\I'\price-dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067995DF-7B42-4DD4-A5C9-BE2955939EE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2EC9B69-EB36-4A6F-8BDD-25131B80E9FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -658,7 +658,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -670,7 +670,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1010,6 +1009,9 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="41.88671875" customWidth="1"/>
+    <col min="3" max="3" width="34.77734375" customWidth="1"/>
+    <col min="4" max="4" width="37" customWidth="1"/>
+    <col min="5" max="5" width="25.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1062,7 +1064,7 @@
       <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D4" s="1"/>
